--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 бррсч и мррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 бррсч и мррсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\23,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1BAB46-94A1-4597-BAC6-5BB737A824A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A30638-2DAC-4290-8D26-51244E9AA8DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="115">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
-  </si>
-  <si>
-    <t>03,09,26 - нет на заводе / 27,08,26 - нет на заводе</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -381,6 +378,12 @@
   <si>
     <t>28,09,Мар</t>
   </si>
+  <si>
+    <t>24,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе</t>
+  </si>
+  <si>
+    <t>нужно увеличить продажи!!! / 24,09,26 - нет на заводе</t>
+  </si>
 </sst>
 </file>
 
@@ -442,7 +445,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,6 +471,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,7 +516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -529,6 +538,7 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -6621,7 +6631,7 @@
     <col min="27" max="27" width="6.5703125" customWidth="1"/>
     <col min="28" max="29" width="5" customWidth="1"/>
     <col min="30" max="39" width="6" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" customWidth="1"/>
+    <col min="40" max="40" width="19" customWidth="1"/>
     <col min="41" max="42" width="7" customWidth="1"/>
     <col min="43" max="57" width="8" customWidth="1"/>
   </cols>
@@ -6800,31 +6810,31 @@
         <v>16</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>17</v>
@@ -6894,10 +6904,10 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="1"/>
@@ -6916,28 +6926,28 @@
       <c r="R4" s="1"/>
       <c r="S4" s="15"/>
       <c r="T4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="X4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="Y4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="V4" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="Z4" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
@@ -6973,10 +6983,10 @@
       </c>
       <c r="AN4" s="1"/>
       <c r="AO4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP4" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
@@ -7070,7 +7080,7 @@
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="2"/>
-        <v>3440</v>
+        <v>3416</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="2"/>
@@ -7258,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="AN6" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AO6" s="1">
         <f>H6*U6</f>
@@ -7752,9 +7762,8 @@
         <f t="shared" ref="Y10:Y56" si="11">X10</f>
         <v>12</v>
       </c>
-      <c r="Z10" s="5">
-        <f>VLOOKUP(A10,Мариуполь!A:B,2,0)</f>
-        <v>12</v>
+      <c r="Z10" s="21">
+        <v>0</v>
       </c>
       <c r="AA10" s="5">
         <f>VLOOKUP(A10,[2]Sheet!$A:$W,23,0)</f>
@@ -7799,7 +7808,7 @@
         <v>5.2</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="AO10" s="1">
         <f t="shared" si="9"/>
@@ -7827,7 +7836,7 @@
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>35</v>
@@ -7885,9 +7894,8 @@
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="Z11" s="5">
-        <f>VLOOKUP(A11,Мариуполь!A:B,2,0)</f>
-        <v>12</v>
+      <c r="Z11" s="21">
+        <v>0</v>
       </c>
       <c r="AA11" s="5">
         <f>VLOOKUP(A11,[2]Sheet!$A:$W,23,0)</f>
@@ -7932,7 +7940,7 @@
         <v>3</v>
       </c>
       <c r="AN11" s="20" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="AO11" s="1">
         <f t="shared" si="9"/>
@@ -7960,7 +7968,7 @@
     </row>
     <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>39</v>
@@ -8096,7 +8104,7 @@
     </row>
     <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>35</v>
@@ -8205,7 +8213,7 @@
         <v>2.8</v>
       </c>
       <c r="AN13" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AO13" s="1">
         <f t="shared" si="9"/>
@@ -8233,7 +8241,7 @@
     </row>
     <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
@@ -8374,7 +8382,7 @@
     </row>
     <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -8522,7 +8530,7 @@
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -8668,7 +8676,7 @@
     </row>
     <row r="17" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>35</v>
@@ -8778,7 +8786,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AO17" s="1">
         <f t="shared" si="9"/>
@@ -8806,7 +8814,7 @@
     </row>
     <row r="18" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>35</v>
@@ -8949,7 +8957,7 @@
     </row>
     <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>35</v>
@@ -9095,7 +9103,7 @@
     </row>
     <row r="20" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>35</v>
@@ -9237,7 +9245,7 @@
     </row>
     <row r="21" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -9379,7 +9387,7 @@
     </row>
     <row r="22" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -9523,7 +9531,7 @@
     </row>
     <row r="23" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -9641,7 +9649,7 @@
         <v>97.8</v>
       </c>
       <c r="AN23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AO23" s="1">
         <f t="shared" si="9"/>
@@ -9669,7 +9677,7 @@
     </row>
     <row r="24" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -9775,7 +9783,7 @@
         <v>2.6</v>
       </c>
       <c r="AN24" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO24" s="1">
         <f t="shared" si="9"/>
@@ -9803,7 +9811,7 @@
     </row>
     <row r="25" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
@@ -9905,7 +9913,7 @@
         <v>0.2</v>
       </c>
       <c r="AN25" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO25" s="1">
         <f t="shared" si="9"/>
@@ -9933,7 +9941,7 @@
     </row>
     <row r="26" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -10038,7 +10046,7 @@
         <v>3.6</v>
       </c>
       <c r="AN26" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO26" s="1">
         <f t="shared" si="9"/>
@@ -10066,7 +10074,7 @@
     </row>
     <row r="27" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -10167,7 +10175,7 @@
         <v>0</v>
       </c>
       <c r="AN27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AO27" s="1">
         <f t="shared" si="9"/>
@@ -10195,7 +10203,7 @@
     </row>
     <row r="28" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>39</v>
@@ -10288,7 +10296,7 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="AN28" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO28" s="1">
         <f t="shared" si="9"/>
@@ -10316,7 +10324,7 @@
     </row>
     <row r="29" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>39</v>
@@ -10418,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="AN29" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO29" s="1">
         <f t="shared" si="9"/>
@@ -10446,7 +10454,7 @@
     </row>
     <row r="30" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>35</v>
@@ -10558,7 +10566,7 @@
         <v>4.2</v>
       </c>
       <c r="AN30" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AO30" s="1">
         <f t="shared" si="9"/>
@@ -10586,7 +10594,7 @@
     </row>
     <row r="31" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>35</v>
@@ -10719,7 +10727,7 @@
     </row>
     <row r="32" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>35</v>
@@ -10855,7 +10863,7 @@
     </row>
     <row r="33" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -10991,7 +10999,7 @@
     </row>
     <row r="34" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -11100,7 +11108,7 @@
         <v>29</v>
       </c>
       <c r="AN34" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AO34" s="1">
         <f t="shared" si="9"/>
@@ -11128,7 +11136,7 @@
     </row>
     <row r="35" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -11264,7 +11272,7 @@
     </row>
     <row r="36" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
@@ -11370,7 +11378,7 @@
         <v>0.4</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AO36" s="1">
         <f t="shared" si="9"/>
@@ -11398,7 +11406,7 @@
     </row>
     <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>35</v>
@@ -11516,7 +11524,7 @@
         <v>17.2</v>
       </c>
       <c r="AN37" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AO37" s="1">
         <f t="shared" si="9"/>
@@ -11544,7 +11552,7 @@
     </row>
     <row r="38" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>35</v>
@@ -11691,7 +11699,7 @@
     </row>
     <row r="39" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>35</v>
@@ -11834,7 +11842,7 @@
     </row>
     <row r="40" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>35</v>
@@ -11951,7 +11959,7 @@
         <v>2.8</v>
       </c>
       <c r="AN40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AO40" s="1">
         <f t="shared" si="9"/>
@@ -11979,7 +11987,7 @@
     </row>
     <row r="41" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -12120,7 +12128,7 @@
     </row>
     <row r="42" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -12263,7 +12271,7 @@
     </row>
     <row r="43" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>39</v>
@@ -12289,7 +12297,7 @@
         <v>180</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1">
@@ -12370,7 +12378,7 @@
         <v>1.2356</v>
       </c>
       <c r="AN43" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AO43" s="1">
         <f t="shared" si="9"/>
@@ -12398,7 +12406,7 @@
     </row>
     <row r="44" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>39</v>
@@ -12542,7 +12550,7 @@
     </row>
     <row r="45" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>39</v>
@@ -12563,7 +12571,7 @@
       </c>
       <c r="I45" s="11"/>
       <c r="J45" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>38</v>
@@ -12669,7 +12677,7 @@
     </row>
     <row r="46" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>39</v>
@@ -12807,7 +12815,7 @@
     </row>
     <row r="47" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>39</v>
@@ -12916,7 +12924,7 @@
         <v>0.60640000000000005</v>
       </c>
       <c r="AN47" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AO47" s="1">
         <f t="shared" si="9"/>
@@ -12944,7 +12952,7 @@
     </row>
     <row r="48" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -13090,7 +13098,7 @@
     </row>
     <row r="49" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>35</v>
@@ -13236,7 +13244,7 @@
     </row>
     <row r="50" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -13383,7 +13391,7 @@
     </row>
     <row r="51" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
@@ -13527,7 +13535,7 @@
     </row>
     <row r="52" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>39</v>
@@ -13552,7 +13560,7 @@
         <v>120</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1">
@@ -13640,7 +13648,7 @@
         <v>64.421999999999997</v>
       </c>
       <c r="AN52" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO52" s="1">
         <f t="shared" si="9"/>
@@ -13668,7 +13676,7 @@
     </row>
     <row r="53" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>35</v>
@@ -13815,7 +13823,7 @@
     </row>
     <row r="54" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>35</v>
@@ -13836,10 +13844,10 @@
       </c>
       <c r="I54" s="11"/>
       <c r="J54" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L54" s="11">
         <v>1</v>
@@ -13942,7 +13950,7 @@
     </row>
     <row r="55" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>39</v>
@@ -13963,10 +13971,10 @@
       </c>
       <c r="I55" s="11"/>
       <c r="J55" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L55" s="11"/>
       <c r="M55" s="11">
@@ -14067,7 +14075,7 @@
     </row>
     <row r="56" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>39</v>
@@ -40436,7 +40444,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>16</v>
@@ -40444,7 +40452,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>96</v>
@@ -40452,7 +40460,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>144</v>
@@ -40460,7 +40468,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>216</v>
@@ -40468,7 +40476,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8">
         <v>300</v>
@@ -40476,7 +40484,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>96</v>
@@ -40484,7 +40492,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>16</v>
@@ -40492,7 +40500,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>144</v>
@@ -40500,7 +40508,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>48</v>
@@ -40508,7 +40516,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13">
         <v>16</v>
@@ -40516,7 +40524,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14">
         <v>1000</v>
@@ -40524,7 +40532,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15">
         <v>1000</v>
@@ -40532,7 +40540,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>78</v>
@@ -40540,7 +40548,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17">
         <v>48</v>
@@ -40548,7 +40556,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>200</v>
@@ -40556,7 +40564,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -40564,7 +40572,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20">
         <v>50</v>
@@ -40572,7 +40580,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21">
         <v>120</v>
@@ -40580,7 +40588,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22">
         <v>500</v>
@@ -40588,7 +40596,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23">
         <v>200</v>
@@ -40596,7 +40604,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24">
         <v>8</v>
@@ -40604,7 +40612,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25">
         <v>96</v>
@@ -40612,7 +40620,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26">
         <v>128</v>
@@ -40620,7 +40628,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27">
         <v>16</v>
@@ -40628,7 +40636,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28">
         <v>50</v>
@@ -40636,7 +40644,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29">
         <v>420</v>
@@ -40644,7 +40652,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30">
         <v>252</v>
@@ -40652,7 +40660,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31">
         <v>112</v>
@@ -40660,7 +40668,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32">
         <v>30</v>
@@ -40668,7 +40676,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -40726,7 +40734,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>12</v>
@@ -40734,7 +40742,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>33</v>
@@ -40742,7 +40750,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>24</v>
@@ -40750,7 +40758,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>96</v>
@@ -40758,7 +40766,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>96</v>
@@ -40766,7 +40774,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>180</v>
@@ -40774,7 +40782,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>144</v>
@@ -40782,7 +40790,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>16</v>
@@ -40790,7 +40798,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>16</v>
@@ -40798,7 +40806,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>16</v>
@@ -40806,7 +40814,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>500</v>
@@ -40814,7 +40822,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>500</v>
@@ -40822,7 +40830,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -40830,7 +40838,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19">
         <v>28</v>
@@ -40838,7 +40846,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20">
         <v>24</v>
@@ -40846,7 +40854,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -40854,7 +40862,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22">
         <v>102</v>
@@ -40862,7 +40870,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23">
         <v>128</v>
@@ -40870,7 +40878,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24">
         <v>128</v>
@@ -40878,7 +40886,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -40886,7 +40894,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26">
         <v>150</v>
@@ -40894,7 +40902,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B27">
         <v>30</v>
@@ -40902,7 +40910,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -40910,7 +40918,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29">
         <v>150</v>
@@ -40918,7 +40926,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30">
         <v>50</v>
@@ -40926,7 +40934,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31">
         <v>8</v>
@@ -40934,7 +40942,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32">
         <v>32</v>
@@ -40942,7 +40950,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33">
         <v>48</v>
@@ -40950,7 +40958,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34">
         <v>16</v>
@@ -40958,7 +40966,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35">
         <v>99</v>
@@ -40966,7 +40974,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36">
         <v>16</v>
@@ -40974,7 +40982,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37">
         <v>300</v>
@@ -40982,7 +40990,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38">
         <v>150</v>
@@ -40990,7 +40998,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39">
         <v>16</v>
@@ -40998,7 +41006,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -41006,7 +41014,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B41">
         <v>15</v>
@@ -41014,7 +41022,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42">
         <v>10</v>
@@ -41022,7 +41030,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43">
         <v>15</v>
